--- a/artfynd/A 37604-2026 artfynd.xlsx
+++ b/artfynd/A 37604-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042879</v>
       </c>
       <c r="B2" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042880</v>
       </c>
       <c r="B3" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136481249</v>
       </c>
       <c r="B4" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136481251</v>
       </c>
       <c r="B5" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136481257</v>
       </c>
       <c r="B6" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37604-2026 artfynd.xlsx
+++ b/artfynd/A 37604-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042879</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042880</v>
       </c>
       <c r="B3" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136481249</v>
       </c>
       <c r="B4" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136481251</v>
       </c>
       <c r="B5" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136481257</v>
       </c>
       <c r="B6" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37604-2026 artfynd.xlsx
+++ b/artfynd/A 37604-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136481249</v>
       </c>
       <c r="B4" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136481251</v>
       </c>
       <c r="B5" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136481257</v>
       </c>
       <c r="B6" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136481222</v>
       </c>
       <c r="B10" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37604-2026 artfynd.xlsx
+++ b/artfynd/A 37604-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136481249</v>
       </c>
       <c r="B4" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136481251</v>
       </c>
       <c r="B5" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136481257</v>
       </c>
       <c r="B6" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37604-2026 artfynd.xlsx
+++ b/artfynd/A 37604-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136481249</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136481251</v>
       </c>
       <c r="B5" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136481257</v>
       </c>
       <c r="B6" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136481222</v>
       </c>
       <c r="B10" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37604-2026 artfynd.xlsx
+++ b/artfynd/A 37604-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136481249</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136481251</v>
       </c>
       <c r="B5" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136481257</v>
       </c>
       <c r="B6" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136481222</v>
       </c>
       <c r="B10" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37604-2026 artfynd.xlsx
+++ b/artfynd/A 37604-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136481249</v>
       </c>
       <c r="B4" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136481251</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136481257</v>
       </c>
       <c r="B6" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136481222</v>
       </c>
       <c r="B10" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37604-2026 artfynd.xlsx
+++ b/artfynd/A 37604-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136481249</v>
       </c>
       <c r="B4" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136481251</v>
       </c>
       <c r="B5" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136481257</v>
       </c>
       <c r="B6" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37604-2026 artfynd.xlsx
+++ b/artfynd/A 37604-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136481249</v>
       </c>
       <c r="B4" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136481251</v>
       </c>
       <c r="B5" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136481257</v>
       </c>
       <c r="B6" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136481222</v>
       </c>
       <c r="B10" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
